--- a/Data/g13.2.xlsx
+++ b/Data/g13.2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,7 +973,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>43.73</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>44.01</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>44.04</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1043,11 +1043,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>43.97</v>
+        <v>51.01</v>
       </c>
     </row>
     <row r="32">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>43.51</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="33">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="34">
@@ -1103,11 +1103,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="35">
@@ -1123,11 +1123,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>43.97</v>
       </c>
     </row>
     <row r="36">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="37">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>43.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>43.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1303,11 +1303,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>42.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>42.8</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="46">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>43.48</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="47">
@@ -1363,11 +1363,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>43.37</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="48">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>43.16</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="49">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2023</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>43.34</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="50">
@@ -1423,11 +1423,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2023</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>44.02</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="51">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>44.42</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="52">
@@ -1463,11 +1463,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>43.68</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="53">
@@ -1483,17 +1483,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2024</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>44.07</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1503,17 +1503,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>46.15</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1523,17 +1523,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>47.74</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/07/2019</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>47.39</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1563,17 +1563,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>48.62</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>46.73</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/04/2020</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1623,17 +1623,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/07/2020</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="62">
@@ -1663,11 +1663,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="63">
@@ -1683,11 +1683,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="64">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/07/2021</t>
+          <t>01/07/2019</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="65">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="66">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="67">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>46.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1783,11 +1783,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/07/2020</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>45.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>46.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1823,11 +1823,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>44.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1843,11 +1843,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01/04/2023</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>44.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1863,11 +1863,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01/07/2023</t>
+          <t>01/07/2021</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>45.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>44.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1903,11 +1903,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>46.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/04/2024</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>46.84</v>
+        <v>46.48</v>
       </c>
     </row>
     <row r="76">
@@ -1943,11 +1943,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>46.99</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="77">
@@ -1963,11 +1963,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>46.65</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="78">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>45.21</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="79">
@@ -2003,11 +2003,251 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>01/04/2023</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>44.39</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>01/07/2023</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>45.49</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>46.66</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>46.84</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>46.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>46.65</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>45.21</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D87" t="n">
         <v>44.83</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>43.22</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>45.05</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>45.53</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Taxa de pessoas de 14 anos ou mais de idade, na força de trabalho, na semana de referência</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>45.8</v>
       </c>
     </row>
   </sheetData>
